--- a/Auxiliary Files/Feature Selection.xlsx
+++ b/Auxiliary Files/Feature Selection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/97f316a1632ce539/Documentos/Nova IMS/Tese/Código/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{728ACB7E-081D-4D0A-A7E5-7B4DD0D535D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{728ACB7E-081D-4D0A-A7E5-7B4DD0D535D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A71C5CA3-682E-439B-AB32-D44AB195E62E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F725C4BA-7799-4650-8AE0-E01BC49B4C29}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F725C4BA-7799-4650-8AE0-E01BC49B4C29}"/>
   </bookViews>
   <sheets>
     <sheet name="Admissions" sheetId="1" r:id="rId1"/>
@@ -117,15 +117,6 @@
     <t>AverageAcademicDegree</t>
   </si>
   <si>
-    <t>datacandidaturafim_day_of_week_sin</t>
-  </si>
-  <si>
-    <t>datacandidaturafim_day_of_week_cos</t>
-  </si>
-  <si>
-    <t>dprograma</t>
-  </si>
-  <si>
     <t>Previous_IMS_Student</t>
   </si>
   <si>
@@ -201,33 +192,12 @@
     <t>Previous_Jobs_in_Partners</t>
   </si>
   <si>
-    <t>nivelInglesCompreensao</t>
-  </si>
-  <si>
-    <t>nivelInglesFala</t>
-  </si>
-  <si>
-    <t>nivelInglesEscrita</t>
-  </si>
-  <si>
     <t>HighestAcademicDegree</t>
   </si>
   <si>
-    <t>idgenero</t>
-  </si>
-  <si>
     <t>countries_region</t>
   </si>
   <si>
-    <t>datacandidaturafim_month</t>
-  </si>
-  <si>
-    <t>datacandidaturafim_day</t>
-  </si>
-  <si>
-    <t>datacandidaturafim_time_of_day</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -283,6 +253,36 @@
   </si>
   <si>
     <t>Discard*</t>
+  </si>
+  <si>
+    <t>application_submission_day_of_week_cos</t>
+  </si>
+  <si>
+    <t>application_submission_day_of_week_sin</t>
+  </si>
+  <si>
+    <t>ProgramType</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>EnglishComprehensionLevel</t>
+  </si>
+  <si>
+    <t>EnglishSpeakingLevel</t>
+  </si>
+  <si>
+    <t>EnglishWritingLevel</t>
+  </si>
+  <si>
+    <t>application_submission_month</t>
+  </si>
+  <si>
+    <t>application_submission_day</t>
+  </si>
+  <si>
+    <t>application_submission_time_of_day</t>
   </si>
 </sst>
 </file>
@@ -759,7 +759,7 @@
   <dimension ref="A1:J66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" style="3"/>
     <col min="4" max="4" width="12.44140625" style="3" customWidth="1"/>
@@ -806,28 +806,28 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J2" s="3" t="str">
         <f>IF(COUNTIF(B2:I2, "Keep") / (COUNTIF(B2:I2, "Keep") + COUNTIF(B2:I2, "Discard")) &gt; 0.5, "Keep", "Discard")</f>
@@ -839,28 +839,28 @@
         <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J3" s="3" t="str">
         <f t="shared" ref="J3:J42" si="0">IF(COUNTIF(B3:I3, "Keep") / (COUNTIF(B3:I3, "Keep") + COUNTIF(B3:I3, "Discard")) &gt; 0.5, "Keep", "Discard")</f>
@@ -872,28 +872,28 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J4" s="3" t="str">
         <f t="shared" si="0"/>
@@ -902,63 +902,63 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -967,31 +967,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J7" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1000,31 +1000,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J8" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1033,31 +1033,31 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J9" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1066,31 +1066,31 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J10" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1099,31 +1099,31 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J11" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1132,31 +1132,31 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J12" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1165,31 +1165,31 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J13" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1198,31 +1198,31 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J14" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1231,31 +1231,31 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J15" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1267,28 +1267,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J16" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1300,28 +1300,28 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J17" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1333,28 +1333,28 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J18" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1366,31 +1366,31 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -1398,31 +1398,31 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1430,28 +1430,28 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J21" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1463,28 +1463,28 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J22" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1496,28 +1496,28 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J23" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1529,28 +1529,28 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J24" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1562,28 +1562,28 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J25" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1595,28 +1595,28 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J26" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1628,28 +1628,28 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J27" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1661,28 +1661,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J28" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1691,31 +1691,31 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J29" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1724,31 +1724,31 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J30" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1757,31 +1757,31 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J31" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1790,31 +1790,31 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J32" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1823,31 +1823,31 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J33" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1856,31 +1856,31 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J34" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1889,31 +1889,31 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J35" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1922,31 +1922,31 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J36" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1955,31 +1955,31 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J37" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1988,31 +1988,31 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J38" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2021,31 +2021,31 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J39" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2054,31 +2054,31 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J40" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2087,63 +2087,63 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J42" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2152,31 +2152,31 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J43" s="3" t="str">
         <f t="shared" ref="J43:J66" si="1">IF(COUNTIF(B43:I43, "Keep") / (COUNTIF(B43:I43, "Keep") + COUNTIF(B43:I43, "Discard")) &gt; 0.5, "Keep", "Discard")</f>
@@ -2185,31 +2185,31 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J44" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2218,31 +2218,31 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J45" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2251,31 +2251,31 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J46" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2284,31 +2284,31 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J47" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2317,31 +2317,31 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J48" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2350,31 +2350,31 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J49" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2383,31 +2383,31 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J50" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2416,31 +2416,31 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J51" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2449,31 +2449,31 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J52" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2482,31 +2482,31 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J53" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2515,31 +2515,31 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J54" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2548,31 +2548,31 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J55" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2581,31 +2581,31 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J56" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2614,63 +2614,63 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J58" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2679,31 +2679,31 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J59" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2712,31 +2712,31 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J60" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2745,31 +2745,31 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J61" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2778,63 +2778,63 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J63" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2843,31 +2843,31 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J64" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2876,31 +2876,31 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J65" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2909,31 +2909,31 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J66" s="3" t="str">
         <f t="shared" si="1"/>
@@ -2966,7 +2966,7 @@
   <dimension ref="A1:J66"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
@@ -2979,10 +2979,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>2</v>
@@ -3011,28 +3011,28 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J2" s="3" t="str">
         <f>IF(COUNTIF(B2:I2, "Keep") / (COUNTIF(B2:I2, "Keep") + COUNTIF(B2:I2, "Discard")) &gt; 0.5, "Keep", "Discard")</f>
@@ -3044,28 +3044,28 @@
         <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="str">
         <f t="shared" ref="J3:J66" si="0">IF(COUNTIF(B3:I3, "Keep") / (COUNTIF(B3:I3, "Keep") + COUNTIF(B3:I3, "Discard")) &gt; 0.5, "Keep", "Discard")</f>
@@ -3077,28 +3077,28 @@
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J4" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3107,31 +3107,31 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J5" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3140,31 +3140,31 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3173,31 +3173,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J7" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3206,31 +3206,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J8" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3239,31 +3239,31 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J9" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3272,31 +3272,31 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J10" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3305,31 +3305,31 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J11" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3338,31 +3338,31 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J12" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3371,31 +3371,31 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J13" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3404,31 +3404,31 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J14" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3437,31 +3437,31 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J15" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3473,28 +3473,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J16" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3506,28 +3506,28 @@
         <v>14</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J17" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3539,28 +3539,28 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J18" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3572,31 +3572,31 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -3604,31 +3604,31 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -3636,28 +3636,28 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J21" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3669,28 +3669,28 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J22" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3702,28 +3702,28 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J23" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3735,28 +3735,28 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J24" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3768,28 +3768,28 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J25" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3801,28 +3801,28 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J26" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3834,28 +3834,28 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J27" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3867,28 +3867,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J28" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3897,31 +3897,31 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J29" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3930,31 +3930,31 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J30" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3963,31 +3963,31 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J31" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3996,31 +3996,31 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J32" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4029,31 +4029,31 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J33" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4062,31 +4062,31 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J34" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4095,31 +4095,31 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J35" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4128,31 +4128,31 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J36" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4161,31 +4161,31 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J37" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4194,31 +4194,31 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J38" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4227,31 +4227,31 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J39" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4260,31 +4260,31 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J40" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4293,31 +4293,31 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J41" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4326,31 +4326,31 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J42" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4359,31 +4359,31 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J43" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4392,31 +4392,31 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J44" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4425,31 +4425,31 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J45" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4458,31 +4458,31 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J46" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4491,31 +4491,31 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J47" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4524,31 +4524,31 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J48" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4557,31 +4557,31 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J49" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4590,31 +4590,31 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J50" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4623,31 +4623,31 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J51" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4656,31 +4656,31 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J52" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4689,31 +4689,31 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J53" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4722,31 +4722,31 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J54" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4755,31 +4755,31 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J55" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4788,95 +4788,95 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J58" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4885,31 +4885,31 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J59" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4918,31 +4918,31 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J60" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4951,31 +4951,31 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J61" s="3" t="str">
         <f t="shared" si="0"/>
@@ -4984,63 +4984,63 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J63" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5049,31 +5049,31 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J64" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5082,31 +5082,31 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J65" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5115,31 +5115,31 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J66" s="3" t="str">
         <f t="shared" si="0"/>
